--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C424F4-FC21-4C12-8F95-C8FA1B6A50CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A888FAC-745B-48F0-849F-C8E793B0F18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9230" yWindow="1310" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>3rd August 2025</t>
+    <t>29th August 2025</t>
   </si>
 </sst>
 </file>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A888FAC-745B-48F0-849F-C8E793B0F18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB33286-FE35-48F2-A101-D44783967572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="28800" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>29th August 2025</t>
+    <t>27th September 2025</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB33286-FE35-48F2-A101-D44783967572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1005475-85D7-4610-A76B-EA292FB5F14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="28800" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>27th September 2025</t>
+    <t>21st October 2025</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1005475-85D7-4610-A76B-EA292FB5F14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9097538F-E8CA-4033-84DC-7715D39B9D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>21st October 2025</t>
+    <t>26th October 2025</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9097538F-E8CA-4033-84DC-7715D39B9D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FBF3C01-CA18-440E-A4B0-97C9D8A1E51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>26th October 2025</t>
+    <t>30th October 2025</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FBF3C01-CA18-440E-A4B0-97C9D8A1E51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A8A83A-7EE6-4D76-8C82-6423BA6014F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>30th October 2025</t>
+    <t>3rd November 2025</t>
   </si>
 </sst>
 </file>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A8A83A-7EE6-4D76-8C82-6423BA6014F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87B8EE1-9B5F-4E05-B00B-FE8E02BC7FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>3rd November 2025</t>
+    <t>4th November 2025</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87B8EE1-9B5F-4E05-B00B-FE8E02BC7FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4B763A-569D-4610-9A81-EA607133EF5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>4th November 2025</t>
+    <t>21st November 2025</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4B763A-569D-4610-9A81-EA607133EF5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA0489B-2C07-4604-AEC9-0BB9E7FA6BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>21st November 2025</t>
+    <t>30st November 2025</t>
   </si>
 </sst>
 </file>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA0489B-2C07-4604-AEC9-0BB9E7FA6BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD2D7B6-F822-435B-8CD0-5CA4E5916C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>30st November 2025</t>
+    <t>1st December 2025</t>
   </si>
 </sst>
 </file>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD2D7B6-F822-435B-8CD0-5CA4E5916C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD79C7C8-C440-43B8-AD1E-3D4F24059AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>1st December 2025</t>
+    <t>10th December 2025</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD79C7C8-C440-43B8-AD1E-3D4F24059AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599EE8BD-BBDC-44CF-B6A6-791AB7E57E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>10th December 2025</t>
+    <t>8th January 2026</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599EE8BD-BBDC-44CF-B6A6-791AB7E57E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8367A9A2-121C-4F5B-B0BB-221A15026825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4180" yWindow="4180" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>8th January 2026</t>
+    <t>3rd February 2026</t>
   </si>
 </sst>
 </file>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8367A9A2-121C-4F5B-B0BB-221A15026825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FDEB18-EE74-419D-A1E2-ED0B71E5FF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4180" yWindow="4180" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>3rd February 2026</t>
+    <t>11th February 2026</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FDEB18-EE74-419D-A1E2-ED0B71E5FF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE158091-7C09-496B-8C6A-18FD3C1FDC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>11th February 2026</t>
+    <t>4th March 2026</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE158091-7C09-496B-8C6A-18FD3C1FDC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F16214-B204-4DA8-97BD-306AB7CA08F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>4th March 2026</t>
+    <t>11th March 2026</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F16214-B204-4DA8-97BD-306AB7CA08F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F3BC54-CB84-4253-AC81-FD76C8797C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>11th March 2026</t>
+    <t>2nd April</t>
   </si>
 </sst>
 </file>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F3BC54-CB84-4253-AC81-FD76C8797C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E14F316-B1C4-4C42-A646-BD314EBE314D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>2nd April</t>
+    <t>3rd May 2026</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E14F316-B1C4-4C42-A646-BD314EBE314D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC3A854-F632-41E4-A09D-27FD868F0BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>3rd May 2026</t>
+    <t>6th May 2026</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC3A854-F632-41E4-A09D-27FD868F0BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEC31E9-86DA-46B7-AED0-90D20DE0E735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>6th May 2026</t>
+    <t>15th May 2026</t>
   </si>
 </sst>
 </file>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEC31E9-86DA-46B7-AED0-90D20DE0E735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1471B451-D9FE-45DE-8294-26907268B46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>15th May 2026</t>
+    <t>18th May 2026</t>
   </si>
 </sst>
 </file>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1471B451-D9FE-45DE-8294-26907268B46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39D8BEC-D549-4933-BB58-41FDE7B4CB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>18th May 2026</t>
+    <t>26th May 2026</t>
   </si>
 </sst>
 </file>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39D8BEC-D549-4933-BB58-41FDE7B4CB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C29B038-1F6B-473A-A6DC-3E11C2F44680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>26th May 2026</t>
+    <t>23rd June 2026</t>
   </si>
 </sst>
 </file>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C29B038-1F6B-473A-A6DC-3E11C2F44680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3755DE81-A201-48CB-A403-CC369400E914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>23rd June 2026</t>
+    <t>29th June 2026</t>
   </si>
 </sst>
 </file>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3755DE81-A201-48CB-A403-CC369400E914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C9A038-FEED-4891-98AB-9447D468E6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>29th June 2026</t>
+    <t>6th August 2026</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C9A038-FEED-4891-98AB-9447D468E6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C256DA35-85D8-4D58-BE65-1E572535DCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>6th August 2026</t>
+    <t>9th August 2026</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C256DA35-85D8-4D58-BE65-1E572535DCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3D4CC8-146D-435E-B73D-0A48994CB299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>9th August 2026</t>
+    <t>21st August 2026</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3D4CC8-146D-435E-B73D-0A48994CB299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB6109B-4B19-40BA-A01F-92D6D664BC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>21st August 2026</t>
+    <t>22nd August 2026</t>
   </si>
 </sst>
 </file>
